--- a/data/seed/portfolio/L-2024-7409/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-7409/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J172"/>
+  <dimension ref="A1:J179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -535,237 +535,237 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B8" t="n">
         <v>100</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>31717000</v>
+        <v>43460000</v>
       </c>
       <c r="D8" s="2" t="n"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bekobod Mebel MChJ</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>264968280</t>
+          <t>379231023</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000071946587001</t>
+          <t>20208000827805746001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №272/26, QQS bilan</t>
+          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №48/26, QQS BILAN</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>192083000</v>
+        <v>180340000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46206</v>
+        <v>46204</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n">
-        <v>19674000</v>
-      </c>
+      <c r="C9" s="2" t="n">
+        <v>91336000</v>
+      </c>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Guliston Agro AJ</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>311518277</t>
+          <t>379231023</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000026703389001</t>
+          <t>20208000827805746001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, H/F №7718 03.07.2026, QQS BILAN</t>
+          <t>Оплата за сырье по дог. №117/26 от 01.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>211757000</v>
+        <v>89004000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>9891000</v>
+        <v>41606000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>372999048</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000377016016001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №4024 от 03.07.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №359</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>221648000</v>
+        <v>130610000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46208</v>
+        <v>46206</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>67100000</v>
-      </c>
-      <c r="D11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n">
+        <v>13908000</v>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-7409)</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>16307000309003328417</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-7409 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2448 03.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>154548000</v>
+        <v>144518000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>81200000</v>
+        <v>12526000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Sharq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>372999048</t>
+          <t>360269719</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000377016016001</t>
+          <t>20208000398158286001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №8079 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchunto'lov, h/f №8977 03.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>235748000</v>
+        <v>157044000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46209</v>
+        <v>46208</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n">
-        <v>29561000</v>
-      </c>
+      <c r="C13" s="2" t="n">
+        <v>67100000</v>
+      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chust Non XK</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>332698024</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-7409)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000665385518001</t>
+          <t>16307000309003328417</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5288</t>
+          <t>Kredit shartnomasi L-2024-7409 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>265309000</v>
+        <v>89944000</v>
       </c>
     </row>
     <row r="14">
@@ -775,23 +775,18 @@
       <c r="B14" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
-        <v>12694000</v>
-      </c>
+      <c r="C14" s="2" t="n">
+        <v>65392000</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Guliston Agro AJ</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>311518277</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000026703389001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -801,11 +796,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9827 за поставленный товар</t>
+          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>278003000</v>
+        <v>24552000</v>
       </c>
     </row>
     <row r="15">
@@ -815,63 +810,63 @@
       <c r="B15" t="n">
         <v>107</v>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n">
-        <v>8167000</v>
-      </c>
+      <c r="C15" s="2" t="n">
+        <v>119855000</v>
+      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Yulduz Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>372999048</t>
+          <t>257480577</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000377016016001</t>
+          <t>20208000761482579001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Shartnoma №157/26 bo'yicha oldindan to'lov</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №64/26</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>286170000</v>
+        <v>-95303000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>7836000</v>
+        <v>31097000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zafar Agro Servis MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>370484950</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000021089814001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -881,131 +876,136 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №3431 06.07.2026, QQS BILAN</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №309</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>294006000</v>
+        <v>-64206000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>65392000</v>
-      </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n">
+        <v>25319000</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №1332</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9224 09.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>228614000</v>
+        <v>-38887000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n">
-        <v>38916000</v>
+        <v>11895000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Farg'ona Metall Servis AJ</t>
+          <t>Marg'ilon Moy MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>269636970</t>
+          <t>251827760</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000947942766001</t>
+          <t>20208000670338952001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1404</t>
+          <t>Tovar uchun to'lov, h/f №4872 09.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>267530000</v>
+        <v>-26992000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n">
-        <v>11175000</v>
+        <v>9028000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №254/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1841</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>278705000</v>
+        <v>-17964000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
@@ -1016,22 +1016,22 @@
       <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bahor Qurilish MChJ</t>
+          <t>Gulshan Qurilish AJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>344962824</t>
+          <t>312120063</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000483051248001</t>
+          <t>20208000982337028001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1040,167 +1040,167 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>270327000</v>
+        <v>-26342000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>45372000</v>
-      </c>
-      <c r="D21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n">
+        <v>15369000</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bekobod Mebel MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>264968280</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000071946587001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №160/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6987 10.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>224955000</v>
+        <v>-10973000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>277875000</v>
+        <v>10231000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Olmaliq Metall Servis XK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>325999899</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000699838757001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №197 09.07.2026, QQS bilan</t>
+          <t>Shartnoma №123/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>502830000</v>
+        <v>-742000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="2" t="n">
-        <v>66229000</v>
+        <v>93078000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №32/26, QQS 12%</t>
+          <t>Shartnoma №41/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>569059000</v>
+        <v>92336000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
-        <v>22698000</v>
+        <v>26573000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Olmaliq Metall Servis XK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>325999899</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000699838757001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9781 10.07.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9950 13.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>591757000</v>
+        <v>118909000</v>
       </c>
     </row>
     <row r="25">
@@ -1212,35 +1212,35 @@
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>26606000</v>
+        <v>9234000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Shartnoma №220/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №202/26, QQS 12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>618363000</v>
+        <v>128143000</v>
       </c>
     </row>
     <row r="26">
@@ -1250,23 +1250,23 @@
       <c r="B26" t="n">
         <v>118</v>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>11925000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>12293000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Angren Plastik MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>363697009</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000794276620001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1276,37 +1276,37 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №202/26, QQS 12%</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №1468</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>630288000</v>
+        <v>115850000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
-        <v>29173000</v>
-      </c>
+      <c r="C27" s="2" t="n">
+        <v>12672000</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>379231023</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000827805746001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1316,37 +1316,37 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №276/26 от 14.07.2026</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №3/26</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>659461000</v>
+        <v>103178000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n">
-        <v>10344000</v>
-      </c>
+      <c r="C28" s="2" t="n">
+        <v>37269000</v>
+      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>379231023</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000827805746001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1356,37 +1356,37 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2503 за поставленный товар</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №127/26, QQS bilan</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>669805000</v>
+        <v>65909000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n">
-        <v>19670000</v>
-      </c>
+      <c r="C29" s="2" t="n">
+        <v>214857000</v>
+      </c>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>379231023</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000827805746001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1396,96 +1396,96 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Tovar uchn to'lov, hisob-faktura №4774 15.07.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору №254/26</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>689475000</v>
+        <v>-148948000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n">
-        <v>14384000</v>
+        <v>63148000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Navro'z Sut MChJ</t>
+          <t>Nurafshon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>361212006</t>
+          <t>299904893</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000098233702001</t>
+          <t>20208000701601614001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9537 от 15.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №81/26 от 14.07.2026</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>703859000</v>
+        <v>-85800000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46219</v>
+        <v>46217</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>8917000</v>
-      </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n">
+        <v>22773000</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Sharq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>360269719</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000398158286001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyun 2026</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №241/26, QQS 12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>694942000</v>
+        <v>-63027000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46219</v>
+        <v>46217</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
@@ -1516,251 +1516,251 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>JShDS iyun oyi uchun</t>
+          <t>Ijtimoiy soliq iyun 2026</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>686025000</v>
+        <v>-71944000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46219</v>
+        <v>46217</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>40702000</v>
+        <v>8917000</v>
       </c>
       <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bekobod Mebel MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>264968280</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000071946587001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №982</t>
+          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>645323000</v>
+        <v>-80861000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46219</v>
+        <v>46217</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>457101000</v>
+        <v>97218000</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mehnat Metall Servis AJ</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>396396108</t>
+          <t>379231023</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000901779336001</t>
+          <t>20208000827805746001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №115/26, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №168/26</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>188222000</v>
+        <v>-178079000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n">
-        <v>25405000</v>
+        <v>54552000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5747</t>
+          <t>Tovar uchun to'lov, h/f №688 16.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>213627000</v>
+        <v>-123527000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>27659000</v>
-      </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n">
+        <v>17226000</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Namangan Moy MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321812203</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000102858181001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2550</t>
+          <t>Оплата за продукцию по договору №21/26, НДС 12%</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>185968000</v>
+        <v>-106301000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>39318000</v>
+        <v>80124000</v>
       </c>
       <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bekobod Mebel MChJ</t>
+          <t>Angren Logistik MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>264968280</t>
+          <t>266155988</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000071946587001</t>
+          <t>20208000649237110001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №1/26, QQS bilan</t>
+          <t>Предоплата за материалы по договору №7/26</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>146650000</v>
+        <v>-186425000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>129841000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>49427000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Jizzax Poligraf XK</t>
+          <t>Sharq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>214270950</t>
+          <t>360269719</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000940021094001</t>
+          <t>20208000398158286001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №142/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №94/26, QQS 12%</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>16809000</v>
+        <v>-136998000</v>
       </c>
     </row>
     <row r="39">
@@ -1772,35 +1772,35 @@
       </c>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n">
-        <v>63723000</v>
+        <v>19506000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №650 20.07.2026, QQS bilan</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №6599 20.07.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>80532000</v>
+        <v>-117492000</v>
       </c>
     </row>
     <row r="40">
@@ -1812,35 +1812,35 @@
       </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n">
-        <v>39390000</v>
+        <v>19216000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Nurafshon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>299904893</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000701601614001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3357 за поставленны товар</t>
+          <t>Mahsulot uchun to'lov, shartnoma №44/26, QQS 12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>119922000</v>
+        <v>-98276000</v>
       </c>
     </row>
     <row r="41">
@@ -1850,37 +1850,37 @@
       <c r="B41" t="n">
         <v>133</v>
       </c>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n">
-        <v>18550000</v>
-      </c>
+      <c r="C41" s="2" t="n">
+        <v>26753000</v>
+      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Guliston Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>322394072</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000620763419001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9531 20.07.2026, QQS bilan</t>
+          <t>Transport xzmatlari uchun to'lov, shartnoma №267/26</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>138472000</v>
+        <v>-125029000</v>
       </c>
     </row>
     <row r="42">
@@ -1890,37 +1890,37 @@
       <c r="B42" t="n">
         <v>134</v>
       </c>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n">
-        <v>11029000</v>
-      </c>
+      <c r="C42" s="2" t="n">
+        <v>29046000</v>
+      </c>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chust Non XK</t>
+          <t>Angren Plastik MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>332698024</t>
+          <t>363697009</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000665385518001</t>
+          <t>20208000794276620001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1728 20.07.2026, QQS bilan</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №4396</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>149501000</v>
+        <v>-154075000</v>
       </c>
     </row>
     <row r="43">
@@ -1930,223 +1930,223 @@
       <c r="B43" t="n">
         <v>135</v>
       </c>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n">
-        <v>7797000</v>
-      </c>
+      <c r="C43" s="2" t="n">
+        <v>70588000</v>
+      </c>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ilhom Sut XK</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>275259998</t>
+          <t>379231023</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000906998387001</t>
+          <t>20208000827805746001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №8459 20.07.2026, QQS bilan</t>
+          <t>Tovarlar uchun to'lov h/f №9788</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>157298000</v>
+        <v>-224663000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>72876000</v>
+        <v>108098000</v>
       </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Meva Eksport MChJ</t>
+          <t>Angren Logistik MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>208702481</t>
+          <t>266155988</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000719243557001</t>
+          <t>20208000649237110001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №13/26</t>
+          <t>Оплата за товары согласно счет-фактуре №6950</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>84422000</v>
+        <v>-332761000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>18269000</v>
+        <v>222902000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Nurafshon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>372999048</t>
+          <t>299904893</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000377016016001</t>
+          <t>20208000701601614001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8209</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3659</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>102691000</v>
+        <v>-109859000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>14213000</v>
-      </c>
-      <c r="D46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n">
+        <v>38961000</v>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>QQS iyun 2026 uchun</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3261 22.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>88478000</v>
+        <v>-70898000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n">
-        <v>29529000</v>
+        <v>10507000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №70/26, QQS 12%</t>
+          <t>Оплата по счет-фактуре №4486 за поставленный товар</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>118007000</v>
+        <v>-60391000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46227</v>
+        <v>46226</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>5237000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>12111000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000034886665001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2156,51 +2156,51 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov iyul</t>
+          <t>Оплата за товар по счет-фактуре №2181 от 23.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>112770000</v>
+        <v>-48280000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46230</v>
+        <v>46226</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>17694000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>13806000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Zafar Agro Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>370484950</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000021089814001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договор №104/26, НДС 12%</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>130464000</v>
+        <v>-62086000</v>
       </c>
     </row>
     <row r="50">
@@ -2212,35 +2212,35 @@
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>10016000</v>
+        <v>48224000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Shartnoma №117/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8380</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>140480000</v>
+        <v>-13862000</v>
       </c>
     </row>
     <row r="51">
@@ -2252,35 +2252,35 @@
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>8018000</v>
+        <v>27041000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>372999048</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000377016016001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4141 27.07.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №4583 за поставленный товар</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>148498000</v>
+        <v>13179000</v>
       </c>
     </row>
     <row r="52">
@@ -2290,103 +2290,103 @@
       <c r="B52" t="n">
         <v>144</v>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>117127000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>26322000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Namangan Moy MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>321812203</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000102858181001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №254/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6161</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>31371000</v>
+        <v>39501000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>15036000</v>
+        <v>13441000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Qo'qon Qog'oz MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>313713960</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000520356575001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8305 28.07.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1455 27.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>46407000</v>
+        <v>52942000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46232</v>
+        <v>46230</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>39862000</v>
+        <v>13288000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Sharq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>360269719</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000398158286001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2396,197 +2396,197 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Shartnoma №291/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по с/ф №1642 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>86269000</v>
+        <v>66230000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n">
-        <v>34137000</v>
-      </c>
+      <c r="C55" s="2" t="n">
+        <v>5237000</v>
+      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Navoiy Moy MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>356602697</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000943981582001</t>
+          <t>20208000827594500001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №7072 от 30.07.2026, в т.ч. НДС 12%</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>120406000</v>
+        <v>60993000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46233</v>
+        <v>46231</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n">
-        <v>26851000</v>
-      </c>
+      <c r="C56" s="2" t="n">
+        <v>12711000</v>
+      </c>
+      <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Angren Logistik MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>266155988</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000649237110001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Shartnoma №245/26 bo'yicha oldindan to'lov</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №8223</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>147257000</v>
+        <v>48282000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46234</v>
+        <v>46232</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
       <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="n">
-        <v>77541000</v>
+        <v>86928000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Bunyodkor Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>248495020</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000108981487001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1086 31.07.2026, QQS bilan</t>
+          <t>TOVAR UCHUN TO'LOV, H/F №7929 29.07.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>224798000</v>
+        <v>135210000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46234</v>
+        <v>46232</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>20173000</v>
+        <v>36393000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №686</t>
+          <t>Mahsulot uchun to'lov, shartn. №212/26, QQS 12%</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>244971000</v>
+        <v>171603000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46234</v>
+        <v>46232</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n">
-        <v>13173000</v>
+        <v>10416000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Sharq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>360269719</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000398158286001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2596,166 +2596,166 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7632</t>
+          <t>Оплата за товар по счет-фактуре №4768 от 29.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>258144000</v>
+        <v>182019000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>10195000</v>
+        <v>45480000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>372999048</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000377016016001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>SHARTNOMA №187/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Shartnoma №34/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>268339000</v>
+        <v>227499000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n">
+        <v>12738000</v>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Shartnoma №252/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>268039000</v>
+        <v>240237000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46234</v>
+        <v>46233</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>29893000</v>
+        <v>12180000</v>
       </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Mehnat Metall Servis AJ</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>396396108</t>
+          <t>379231023</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000901779336001</t>
+          <t>20208000827805746001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №187/26</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №132/26, QQS bilan</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>238146000</v>
+        <v>228057000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n">
-        <v>188250000</v>
-      </c>
+      <c r="C63" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ilhom Sut XK</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>275259998</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000906998387001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5117 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>426396000</v>
+        <v>227757000</v>
       </c>
     </row>
     <row r="64">
@@ -2767,35 +2767,35 @@
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>157134000</v>
+        <v>22444000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Nurafshon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>299904893</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000701601614001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №87/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5244</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>583530000</v>
+        <v>250201000</v>
       </c>
     </row>
     <row r="65">
@@ -2807,35 +2807,35 @@
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>15559000</v>
+        <v>11417000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7345 03.08.2026, QQS bilan</t>
+          <t>Shartnoma №212/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>599089000</v>
+        <v>261618000</v>
       </c>
     </row>
     <row r="66">
@@ -2845,23 +2845,23 @@
       <c r="B66" t="n">
         <v>158</v>
       </c>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n">
-        <v>6823000</v>
-      </c>
+      <c r="C66" s="2" t="n">
+        <v>19524000</v>
+      </c>
+      <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>379231023</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000827805746001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2871,11 +2871,11 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4013 03.08.2026, QQS bilan</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №28/26, QQS bilan</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>605912000</v>
+        <v>242094000</v>
       </c>
     </row>
     <row r="67">
@@ -2887,35 +2887,35 @@
       </c>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n">
-        <v>39834000</v>
+        <v>42081000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Qo'qon Qog'oz MChJ</t>
+          <t>Olmaliq Metall Servis XK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>313713960</t>
+          <t>325999899</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000520356575001</t>
+          <t>20208000699838757001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9200 от 04.08.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5406</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>645746000</v>
+        <v>284175000</v>
       </c>
     </row>
     <row r="68">
@@ -2927,35 +2927,35 @@
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>39174000</v>
+        <v>19765000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №216/26, НДС 12%</t>
+          <t>Shartnoma №170/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>684920000</v>
+        <v>303940000</v>
       </c>
     </row>
     <row r="69">
@@ -2966,41 +2966,41 @@
         <v>161</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>21063000</v>
+        <v>50022000</v>
       </c>
       <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bekobod Mebel MChJ</t>
+          <t>Angren Logistik MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>264968280</t>
+          <t>266155988</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000071946587001</t>
+          <t>20208000649237110001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №5/26</t>
+          <t>Xom ashyo uchun to'lov, shartn. №145/26, QQS bilan</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>663857000</v>
+        <v>253918000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
@@ -3026,11 +3026,11 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ish haqi, reestr №437</t>
+          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>599112000</v>
+        <v>189173000</v>
       </c>
     </row>
     <row r="71">
@@ -3040,312 +3040,312 @@
       <c r="B71" t="n">
         <v>163</v>
       </c>
-      <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="n">
-        <v>19023000</v>
-      </c>
+      <c r="C71" s="2" t="n">
+        <v>67100000</v>
+      </c>
+      <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>252112210</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-7409)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>16307000309003328417</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №907</t>
+          <t>Kredit shartnomasi L-2024-7409 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>618135000</v>
+        <v>122073000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n">
-        <v>6856000</v>
+        <v>17522000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Marg'ilon Moy MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>251827760</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000670338952001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6159 от 05.08.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №227/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>624991000</v>
+        <v>139595000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
-      <c r="C73" s="2" t="n">
-        <v>19001000</v>
-      </c>
-      <c r="D73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n">
+        <v>11451000</v>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bekobod Mebel MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>264968280</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000071946587001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №71/26</t>
+          <t>Shartnoma №119/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>605990000</v>
+        <v>151046000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>67100000</v>
-      </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n">
+        <v>107754000</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-7409)</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>16307000309003328417</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-7409 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Mahsulot uchun to'lov, shartnoma №23/26, QQS 12%</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>538890000</v>
+        <v>258800000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>373768000</v>
-      </c>
-      <c r="D75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n">
+        <v>61194000</v>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bekobod Mebel MChJ</t>
+          <t>Sharq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>264968280</t>
+          <t>360269719</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000071946587001</t>
+          <t>20208000398158286001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №95/26, QQS bilan</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №3213 10.08.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>165122000</v>
+        <v>319994000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
       <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="n">
-        <v>29162000</v>
+        <v>59315000</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Guliston Agro AJ</t>
+          <t>Sharq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>311518277</t>
+          <t>360269719</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000026703389001</t>
+          <t>20208000398158286001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2885</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3922</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>194284000</v>
+        <v>379309000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
       <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="n">
-        <v>36013000</v>
+        <v>12187000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6319 07.08.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartn. №89/26, QQS 12%</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>230297000</v>
+        <v>391496000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>8296000</v>
-      </c>
-      <c r="D78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n">
+        <v>9879000</v>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bahor Qurilish MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>344962824</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000483051248001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov avgust</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6862 10.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>222001000</v>
+        <v>401375000</v>
       </c>
     </row>
     <row r="79">
@@ -3355,37 +3355,37 @@
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>32229000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>8296000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Qo'qon Qog'oz MChJ</t>
+          <t>Gulshan Qurilish AJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>313713960</t>
+          <t>312120063</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000520356575001</t>
+          <t>20208000982337028001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Shartnoma №296/26 bo'yicha oldindan to'lov</t>
+          <t>IJARA HAQI AVGUST OYI UCHUN, SHARTN. №33/23</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>254230000</v>
+        <v>393079000</v>
       </c>
     </row>
     <row r="80">
@@ -3395,63 +3395,63 @@
       <c r="B80" t="n">
         <v>172</v>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>26088000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>18070000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ilhom Sut XK</t>
+          <t>Termiz Polimer MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>275259998</t>
+          <t>269802486</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000906998387001</t>
+          <t>20208000538551889001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Shartnoma №131/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за транспортные услуги по договору №36/26</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>280318000</v>
+        <v>375009000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
-      <c r="C81" s="2" t="n"/>
-      <c r="D81" s="2" t="n">
-        <v>42264000</v>
-      </c>
+      <c r="C81" s="2" t="n">
+        <v>51809000</v>
+      </c>
+      <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>379231023</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000827805746001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3461,37 +3461,37 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №237/26, QQS 12%</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №414</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>322582000</v>
+        <v>323200000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n">
-        <v>14640000</v>
-      </c>
+      <c r="C82" s="2" t="n">
+        <v>322738000</v>
+      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>379231023</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000827805746001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3501,277 +3501,277 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №8728 12.08.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору 218/26</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>337222000</v>
+        <v>462000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>10610000</v>
+        <v>12836000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №77 от 13.08.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №12/26, QQS 12%</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>347832000</v>
+        <v>13298000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46251</v>
+        <v>46245</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n">
-        <v>30814000</v>
-      </c>
+      <c r="C84" s="2" t="n">
+        <v>89377000</v>
+      </c>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>372999048</t>
+          <t>379231023</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000377016016001</t>
+          <t>20208000827805746001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №20/26 от 17.08.2026</t>
+          <t>Xom ashyo uchun to'lov, shartn. №46/26, QQS bilan</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>378646000</v>
+        <v>-76079000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46251</v>
+        <v>46246</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>12807000</v>
+        <v>21053000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Zafar Agro Servis MChJ</t>
+          <t>Nurafshon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>370484950</t>
+          <t>299904893</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000021089814001</t>
+          <t>20208000701601614001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Shartnoma №20/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №90/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>391453000</v>
+        <v>-55026000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46251</v>
+        <v>46246</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>11096000</v>
+        <v>16921000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>372999048</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000377016016001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4220</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5005 12.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>402549000</v>
+        <v>-38105000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>8829000</v>
+        <v>17049000</v>
       </c>
       <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>379231023</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000827805746001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyul 2026</t>
+          <t>Tovarlar uchun to'lov h/f №6892</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>393720000</v>
+        <v>-55154000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>8829000</v>
+        <v>215488000</v>
       </c>
       <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Angren Logistik MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>266155988</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000649237110001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyul 2026</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №30/26, QQS bilan</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>384891000</v>
+        <v>-270642000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46252</v>
+        <v>46248</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>38642000</v>
+        <v>10994000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Sharq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>360269719</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000398158286001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3781,277 +3781,277 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5190</t>
+          <t>Оплата по с/ф №4849 за поставленный товар</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>423533000</v>
+        <v>-259648000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46252</v>
+        <v>46248</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>18808000</v>
+        <v>8829000</v>
       </c>
       <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bekobod Mebel MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>264968280</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000071946587001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4671</t>
+          <t>Iyul oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>404725000</v>
+        <v>-268477000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46254</v>
+        <v>46248</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n">
-        <v>251275000</v>
-      </c>
+      <c r="C91" s="2" t="n">
+        <v>8829000</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ilhom Sut XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>275259998</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000906998387001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6532</t>
+          <t>Jismoniy shaxslar daromad solig'i iyul 2026</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>656000000</v>
+        <v>-277306000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46254</v>
+        <v>46251</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
       <c r="C92" s="2" t="n"/>
       <c r="D92" s="2" t="n">
-        <v>6823000</v>
+        <v>48638000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9654 20.08.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №260/26, НДС 12%</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>662823000</v>
+        <v>-228668000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46255</v>
+        <v>46251</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n">
-        <v>13848000</v>
-      </c>
-      <c r="D93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n">
+        <v>18913000</v>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
+          <t>Предоплата за товар по договору №149/26 от 17.08.2026</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>648975000</v>
+        <v>-209755000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46255</v>
+        <v>46251</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
-      <c r="C94" s="2" t="n">
-        <v>24326000</v>
-      </c>
-      <c r="D94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n">
+        <v>12765000</v>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bekobod Mebel MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>264968280</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000071946587001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №261/26, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1351</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>624649000</v>
+        <v>-196990000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
-      <c r="C95" s="2" t="n">
-        <v>22989000</v>
-      </c>
-      <c r="D95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n">
+        <v>6804000</v>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bekobod Mebel MChJ</t>
+          <t>Marg'ilon Moy MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>264968280</t>
+          <t>251827760</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000071946587001</t>
+          <t>20208000670338952001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9206</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5390</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>601660000</v>
+        <v>-190186000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46258</v>
+        <v>46252</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>35549000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>17719000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sarbon Polimer MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>318141824</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000434176206001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4061,237 +4061,237 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6598</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6984</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>566111000</v>
+        <v>-172467000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46258</v>
+        <v>46253</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>141797000</v>
-      </c>
-      <c r="D97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n">
+        <v>40835000</v>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Navoiy Qurilish AJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>220995788</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000432649667001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №6500</t>
+          <t>Mahsulot uchun to'lov, shartnoma №45/26, QQS 12%</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>424314000</v>
+        <v>-131632000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46258</v>
+        <v>46253</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
-      <c r="C98" s="2" t="n">
-        <v>206012000</v>
-      </c>
-      <c r="D98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n">
+        <v>10262000</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Navoiy Qurilish AJ</t>
+          <t>Sharq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>220995788</t>
+          <t>360269719</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000432649667001</t>
+          <t>20208000398158286001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №216/26</t>
+          <t>Shartnoma №124/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>218302000</v>
+        <v>-121370000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46260</v>
+        <v>46253</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n">
-        <v>72061000</v>
+        <v>8923000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Shartnoma №28/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №8/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>290363000</v>
+        <v>-112447000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46260</v>
+        <v>46253</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>47110000</v>
-      </c>
-      <c r="D100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n">
+        <v>6511000</v>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Namangan Moy MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>321812203</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000102858181001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №133/26, QQS bilan</t>
+          <t>Shartnoma №100/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>243253000</v>
+        <v>-105936000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46261</v>
+        <v>46254</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>27986000</v>
+        <v>34354000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>372999048</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000377016016001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №236/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8804</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>271239000</v>
+        <v>-71582000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46261</v>
+        <v>46254</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>13853000</v>
+        <v>20354000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Sharq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>360269719</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000398158286001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4301,347 +4301,357 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5466 за поставленный товар</t>
+          <t>SHARTNOMA №5/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>285092000</v>
+        <v>-51228000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46261</v>
+        <v>46255</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>5185000</v>
-      </c>
-      <c r="D103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n">
+        <v>9774000</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Nurafshon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>299904893</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000034886665001</t>
+          <t>20208000701601614001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>ELEKTR ENERGIYASI UCHUN TO'LOV</t>
+          <t>Оплата за продукцию по договору №75/26, НДС 12%</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>279907000</v>
+        <v>-41454000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46265</v>
+        <v>46255</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n">
-        <v>24951000</v>
-      </c>
+      <c r="C104" s="2" t="n">
+        <v>13673000</v>
+      </c>
+      <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №286/26 от 31.08.2026</t>
+          <t>QQS iyul 2026 uchun</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>304858000</v>
+        <v>-55127000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46265</v>
+        <v>46255</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>300000</v>
+        <v>71349000</v>
       </c>
       <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Ziyo Dori-Darmon XK</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>379231023</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000827805746001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Xom ashyo uchun to'lov, shartn. №2/26, QQS bilan</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>304558000</v>
+        <v>-126476000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>68712000</v>
-      </c>
-      <c r="D106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n">
+        <v>217559000</v>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bekobod Mebel MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>264968280</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000071946587001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4932</t>
+          <t>Оплата по счет-фактуре №8858 за поставленный товар</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>235846000</v>
+        <v>91083000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46266</v>
+        <v>46258</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
       <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="n">
-        <v>46371000</v>
+        <v>87945000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №5453 за поставленный товар</t>
+          <t>Mahsulot uchun to'lov, shartnoma №30/26, QQS 12%</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>282217000</v>
+        <v>179028000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46267</v>
+        <v>46258</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>26688000</v>
+        <v>28185000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №581</t>
+          <t>Mahsulot uchun to'lov, shartn. №37/26, QQS 12%</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>308905000</v>
+        <v>207213000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46267</v>
+        <v>46258</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>21090000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>10798000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Jizzax Poligraf XK</t>
+          <t>Nurafshon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>214270950</t>
+          <t>299904893</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000940021094001</t>
+          <t>20208000701601614001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №292/26, QQS BILAN</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8787</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>287815000</v>
+        <v>218011000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46270</v>
+        <v>46258</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
-      <c r="C110" s="2" t="n">
-        <v>67100000</v>
-      </c>
-      <c r="D110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n">
+        <v>7611000</v>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-7409)</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>16307000309003328417</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-7409 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата за продукцию по договору №250/26, НДС 12%</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>220715000</v>
+        <v>225622000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46272</v>
+        <v>46258</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
-      <c r="C111" s="2" t="n"/>
-      <c r="D111" s="2" t="n">
-        <v>68353000</v>
-      </c>
+      <c r="C111" s="2" t="n">
+        <v>11534000</v>
+      </c>
+      <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>379231023</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000827805746001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4651,37 +4661,37 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №79/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №166/26</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>289068000</v>
+        <v>214088000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46272</v>
+        <v>46258</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n">
-        <v>31867000</v>
-      </c>
+      <c r="C112" s="2" t="n">
+        <v>28120000</v>
+      </c>
+      <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>379231023</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000827805746001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4691,37 +4701,37 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №68/26, QQS 12%</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №8399</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>320935000</v>
+        <v>185968000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46272</v>
+        <v>46259</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
-      <c r="C113" s="2" t="n"/>
-      <c r="D113" s="2" t="n">
-        <v>16228000</v>
-      </c>
+      <c r="C113" s="2" t="n">
+        <v>33181000</v>
+      </c>
+      <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>379231023</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000827805746001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4731,77 +4741,77 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1762 07.09.2026, QQS bilan</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №175/26</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>337163000</v>
+        <v>152787000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46272</v>
+        <v>46260</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>12518000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>5185000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>372999048</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000377016016001</t>
+          <t>20208000827594500001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Shartnoma №204/26 bo'yicha oldindan to'lov</t>
+          <t>Elektr energiyasi uchun to'lov avgust</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>349681000</v>
+        <v>147602000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46272</v>
+        <v>46260</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>8595000</v>
-      </c>
+      <c r="C115" s="2" t="n">
+        <v>14432000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Angren Plastik MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>363697009</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000794276620001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -4811,77 +4821,77 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6378</t>
+          <t>Xom ashyo uchun to'lov, shartn. №50/26, QQS bilan</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>358276000</v>
+        <v>133170000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46272</v>
+        <v>46261</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>6774000</v>
+        <v>53299000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Nurafshon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>299904893</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000701601614001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №182/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5556</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>365050000</v>
+        <v>186469000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46272</v>
+        <v>46261</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>8813000</v>
+        <v>13589000</v>
       </c>
       <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bahor Qurilish MChJ</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>344962824</t>
+          <t>379231023</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000483051248001</t>
+          <t>20208000827805746001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4891,152 +4901,152 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov sentyabr</t>
+          <t>Xom ashyo uchun to'lov, shartn. №228/26, QQS blan</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>356237000</v>
+        <v>172880000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>28125000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>34193000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bekobod Mebel MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>264968280</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000071946587001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №7193</t>
+          <t>Shartnoma №263/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>328112000</v>
+        <v>207073000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
-      <c r="C119" s="2" t="n">
-        <v>68785000</v>
-      </c>
-      <c r="D119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n">
+        <v>27186000</v>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Sharq Trans Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>360269719</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000398158286001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ish haqi, reestr №3383</t>
+          <t>Shartnoma №289/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>259327000</v>
+        <v>234259000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46273</v>
+        <v>46265</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n">
-        <v>45505000</v>
-      </c>
+      <c r="C120" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>252112210</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Shartnoma №146/26 bo'yicha oldindan to'lov</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за август</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>304832000</v>
+        <v>233959000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46274</v>
+        <v>46266</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n">
-        <v>139771000</v>
-      </c>
+      <c r="C121" s="2" t="n">
+        <v>14185000</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Angren Plastik MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>363697009</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000794276620001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5046,397 +5056,392 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8042 09.09.2026, QQS bilan</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №268/26</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>444603000</v>
+        <v>219774000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46274</v>
+        <v>46266</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n">
-        <v>99658000</v>
-      </c>
+      <c r="C122" s="2" t="n">
+        <v>124156000</v>
+      </c>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Angren Plastik MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>372999048</t>
+          <t>363697009</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000377016016001</t>
+          <t>20208000794276620001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №173/26, QQS 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №270/26</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>544261000</v>
+        <v>95618000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46274</v>
+        <v>46268</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
       <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="n">
-        <v>25986000</v>
+        <v>148602000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Olmaliq Metall Servis XK</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>325999899</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000699838757001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9365</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №395</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>570247000</v>
+        <v>244220000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>8371000</v>
+        <v>10253000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5055 от 10.09.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3230 03.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>578618000</v>
+        <v>254473000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46276</v>
+        <v>46270</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>62748000</v>
+        <v>67100000</v>
       </c>
       <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bekobod Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>264968280</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-7409)</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000071946587001</t>
+          <t>16307000309003328417</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №24/26, QQS bilan</t>
+          <t>Kredit shartnomasi L-2024-7409 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>515870000</v>
+        <v>187373000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46276</v>
+        <v>46272</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n">
-        <v>93383000</v>
-      </c>
-      <c r="D126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n">
+        <v>32069000</v>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bekobod Mebel MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>264968280</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000071946587001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9243</t>
+          <t>Оплата за товар по счет-фактуре №5518 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>422487000</v>
+        <v>219442000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
       <c r="C127" s="2" t="n"/>
       <c r="D127" s="2" t="n">
-        <v>29971000</v>
+        <v>25593000</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Qo'qon Qog'oz MChJ</t>
+          <t>Sharq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>313713960</t>
+          <t>360269719</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000520356575001</t>
+          <t>20208000398158286001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3833 14.09.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №222/26, QQS 12%</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>452458000</v>
+        <v>245035000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>20679000</v>
+        <v>19231000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>372999048</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000377016016001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9778 14.09.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №268/26, QQS 12%</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>473137000</v>
+        <v>264266000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="n">
-        <v>16968000</v>
+        <v>9962000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Qo'qon Qog'oz MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>313713960</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000520356575001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Shartnoma №206/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7120 07.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>490105000</v>
+        <v>274228000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
-      <c r="C130" s="2" t="n"/>
-      <c r="D130" s="2" t="n">
-        <v>12151000</v>
-      </c>
+      <c r="C130" s="2" t="n">
+        <v>15976000</v>
+      </c>
+      <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>372999048</t>
+          <t>379231023</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000377016016001</t>
+          <t>20208000827805746001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8962</t>
+          <t>Tovarlar uchun to'lov h/f №6740</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>502256000</v>
+        <v>258252000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n">
-        <v>10251000</v>
-      </c>
+      <c r="C131" s="2" t="n">
+        <v>34892000</v>
+      </c>
+      <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Angren Plastik MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>363697009</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000794276620001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5446,437 +5451,432 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №8304 14.09.2026, QQS bilan</t>
+          <t>Tovarlar uchun to'lov h/f №1550</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>512507000</v>
+        <v>223360000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>8792000</v>
-      </c>
+      <c r="C132" s="2" t="n">
+        <v>68785000</v>
+      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>252112210</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9845</t>
+          <t>Avgust oyi uchun ish haqi, reestr №7326</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>521299000</v>
+        <v>154575000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46279</v>
+        <v>46273</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>8685000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>8813000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Gulshan Qurilish AJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>312120063</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000982337028001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №144/26, QQS 12%</t>
+          <t>Ijara haqi sentyabr oyi uchun, shartnoma №33/23</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>529984000</v>
+        <v>145762000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
-      <c r="C134" s="2" t="n">
-        <v>219091000</v>
-      </c>
-      <c r="D134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n">
+        <v>12184000</v>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Navoiy Qurilish AJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>220995788</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000432649667001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5207</t>
+          <t>Shartnoma №63/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>310893000</v>
+        <v>157946000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46280</v>
+        <v>46274</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
       <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="n">
-        <v>32109000</v>
+        <v>9783000</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Nurafshon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>372999048</t>
+          <t>299904893</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000377016016001</t>
+          <t>20208000701601614001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3819</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8441</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>343002000</v>
+        <v>167729000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46281</v>
+        <v>46275</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
       <c r="C136" s="2" t="n"/>
       <c r="D136" s="2" t="n">
-        <v>14825000</v>
+        <v>157792000</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Guliston Agro AJ</t>
+          <t>Bunyodkor Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>311518277</t>
+          <t>248495020</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000026703389001</t>
+          <t>20208000108981487001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8922</t>
+          <t>Shartnoma №205/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>357827000</v>
+        <v>325521000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46281</v>
+        <v>46275</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="n">
-        <v>14397000</v>
+        <v>36698000</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Zafar Agro Servis MChJ</t>
+          <t>Olmaliq Metall Servis XK</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>370484950</t>
+          <t>325999899</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000021089814001</t>
+          <t>20208000699838757001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5721 16.09.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6653 10.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>372224000</v>
+        <v>362219000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46281</v>
+        <v>46275</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
-      <c r="C138" s="2" t="n">
-        <v>9380000</v>
-      </c>
-      <c r="D138" s="2" t="n"/>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="2" t="n">
+        <v>34405000</v>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq avgust 2026</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №7/26 ОТ 10.09.2026</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>362844000</v>
+        <v>396624000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
-      <c r="C139" s="2" t="n">
-        <v>9380000</v>
-      </c>
-      <c r="D139" s="2" t="n"/>
+      <c r="C139" s="2" t="n"/>
+      <c r="D139" s="2" t="n">
+        <v>51490000</v>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>JShDS avgust oyi uchun</t>
+          <t>Mahsulot uchun to'lov, shartnoma №34/26, QQS 12%</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>353464000</v>
+        <v>448114000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46282</v>
+        <v>46276</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
-      <c r="C140" s="2" t="n">
-        <v>27154000</v>
-      </c>
-      <c r="D140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n">
+        <v>13840000</v>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Namangan Moy MChJ</t>
+          <t>Sharq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>321812203</t>
+          <t>360269719</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000102858181001</t>
+          <t>20208000398158286001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8271</t>
+          <t>Shartnoma №238/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>326310000</v>
+        <v>461954000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46283</v>
+        <v>46276</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="n">
-        <v>16075000</v>
+        <v>11779000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Nurafshon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>299904893</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000701601614001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №151/26, QQS 12%</t>
+          <t>Shartnoma №63/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>342385000</v>
+        <v>473733000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46283</v>
+        <v>46279</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
-      <c r="C142" s="2" t="n">
-        <v>26722000</v>
-      </c>
-      <c r="D142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n">
+        <v>37192000</v>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Bekobod Mebel MChJ</t>
+          <t>Nurafshon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>264968280</t>
+          <t>299904893</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000071946587001</t>
+          <t>20208000701601614001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5886,917 +5886,917 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8200</t>
+          <t>Shartnoma №177/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>315663000</v>
+        <v>510925000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46283</v>
+        <v>46279</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
-      <c r="C143" s="2" t="n">
-        <v>69743000</v>
-      </c>
-      <c r="D143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n">
+        <v>8653000</v>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Jizzax Poligraf XK</t>
+          <t>Marg'ilon Moy MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>214270950</t>
+          <t>251827760</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000940021094001</t>
+          <t>20208000670338952001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №125/26, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartn. №110/26, QQS 12%</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>245920000</v>
+        <v>519578000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
-      <c r="C144" s="2" t="n"/>
-      <c r="D144" s="2" t="n">
-        <v>40031000</v>
-      </c>
+      <c r="C144" s="2" t="n">
+        <v>9380000</v>
+      </c>
+      <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>372999048</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000377016016001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №49/26 от 21.09.2026</t>
+          <t>Avgust oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>285951000</v>
+        <v>510198000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>34450000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>9380000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №163/26 от 21.09.2026</t>
+          <t>НДФЛ ЗА АВГУСТ 2026</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>320401000</v>
+        <v>500818000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
-      <c r="C146" s="2" t="n"/>
-      <c r="D146" s="2" t="n">
-        <v>32905000</v>
-      </c>
+      <c r="C146" s="2" t="n">
+        <v>54773000</v>
+      </c>
+      <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Guliston Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>322394072</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000620763419001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8782 21.09.2026, QQS bilan</t>
+          <t>Tovarlar uchun to'lov h/f №4505</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>353306000</v>
+        <v>446045000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46286</v>
+        <v>46280</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
       <c r="C147" s="2" t="n"/>
       <c r="D147" s="2" t="n">
-        <v>17701000</v>
+        <v>14973000</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Ilhom Sut XK</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>275259998</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000906998387001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №271/26, QQS 12%</t>
+          <t>Оплата за продукцию по дог. №130/26, НДС 12%</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>371007000</v>
+        <v>461018000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
       <c r="C148" s="2" t="n"/>
       <c r="D148" s="2" t="n">
-        <v>11304000</v>
+        <v>41851000</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Olmaliq Metall Servis XK</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>325999899</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000699838757001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Shartnoma №1/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartn. №145/26, QQS 12%</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>382311000</v>
+        <v>502869000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
       <c r="C149" s="2" t="n">
-        <v>66390000</v>
+        <v>15283000</v>
       </c>
       <c r="D149" s="2" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Bekobod Mebel MChJ</t>
+          <t>Angren Plastik MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>264968280</t>
+          <t>363697009</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000071946587001</t>
+          <t>20208000794276620001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №56/26</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №7801</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>315921000</v>
+        <v>487586000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
-      <c r="C150" s="2" t="n">
-        <v>117220000</v>
-      </c>
-      <c r="D150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n">
+        <v>19307000</v>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Mehnat Metall Servis AJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>396396108</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000901779336001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4859</t>
+          <t>Оплата по счет-фактуре №3482 за поставленный товар</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>198701000</v>
+        <v>506893000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46287</v>
+        <v>46282</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
       <c r="C151" s="2" t="n"/>
       <c r="D151" s="2" t="n">
-        <v>42697000</v>
+        <v>11144000</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №3450 22.09.2026, QQS BILAN</t>
+          <t>Mahsulot uchun to'lov, shartnoma №87/26, QQS 12%</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>241398000</v>
+        <v>518037000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
       <c r="C152" s="2" t="n"/>
       <c r="D152" s="2" t="n">
-        <v>32652000</v>
+        <v>70843000</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Nurafshon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>372999048</t>
+          <t>299904893</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000377016016001</t>
+          <t>20208000701601614001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №287/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, h/f №634 18.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>274050000</v>
+        <v>588880000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
-      <c r="C153" s="2" t="n">
-        <v>14949000</v>
-      </c>
-      <c r="D153" s="2" t="n"/>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n">
+        <v>50303000</v>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nurafshon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>299904893</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000701601614001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>QQS avgust 2026 uchun</t>
+          <t>Tovar uchun to'lov, h/f №6474 18.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>259101000</v>
+        <v>639183000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
-      <c r="C154" s="2" t="n">
-        <v>45462000</v>
-      </c>
-      <c r="D154" s="2" t="n"/>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n">
+        <v>43003000</v>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Namangan Moy MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>321812203</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000102858181001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6147</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1227</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>213639000</v>
+        <v>682186000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B155" t="n">
         <v>247</v>
       </c>
-      <c r="C155" s="2" t="n">
-        <v>54763000</v>
-      </c>
-      <c r="D155" s="2" t="n"/>
+      <c r="C155" s="2" t="n"/>
+      <c r="D155" s="2" t="n">
+        <v>59816000</v>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Meva Eksport MChJ</t>
+          <t>Nurafshon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>208702481</t>
+          <t>299904893</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000719243557001</t>
+          <t>20208000701601614001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №171/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9364</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>158876000</v>
+        <v>742002000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>46287</v>
+        <v>46286</v>
       </c>
       <c r="B156" t="n">
         <v>248</v>
       </c>
-      <c r="C156" s="2" t="n">
-        <v>63415000</v>
-      </c>
-      <c r="D156" s="2" t="n"/>
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n">
+        <v>32674000</v>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Bekobod Mebel MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>264968280</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000071946587001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №244/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2479 21.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>95461000</v>
+        <v>774676000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="B157" t="n">
         <v>249</v>
       </c>
       <c r="C157" s="2" t="n"/>
       <c r="D157" s="2" t="n">
-        <v>10983000</v>
+        <v>29121000</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Sharq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>372999048</t>
+          <t>360269719</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000377016016001</t>
+          <t>20208000398158286001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Shartnoma №180/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartn. №266/26, QQS 12%</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>106444000</v>
+        <v>803797000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="B158" t="n">
         <v>250</v>
       </c>
       <c r="C158" s="2" t="n"/>
       <c r="D158" s="2" t="n">
-        <v>78871000</v>
+        <v>12064000</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Ilhom Sut XK</t>
+          <t>Nurafshon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>275259998</t>
+          <t>299904893</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000906998387001</t>
+          <t>20208000701601614001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №93/26, НДС 12%</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №365 21.09.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>185315000</v>
+        <v>815861000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="B159" t="n">
         <v>251</v>
       </c>
-      <c r="C159" s="2" t="n"/>
-      <c r="D159" s="2" t="n">
-        <v>14345000</v>
-      </c>
+      <c r="C159" s="2" t="n">
+        <v>13785000</v>
+      </c>
+      <c r="D159" s="2" t="n"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>372999048</t>
+          <t>379231023</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000377016016001</t>
+          <t>20208000827805746001</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №188/26 ОТ 24.09.2026</t>
+          <t>Tovarlar uchun to'lov h/f №5957</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>199660000</v>
+        <v>802076000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="B160" t="n">
         <v>252</v>
       </c>
       <c r="C160" s="2" t="n"/>
       <c r="D160" s="2" t="n">
-        <v>44970000</v>
+        <v>76589000</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №6351 25.09.2026, QQS BILAN</t>
+          <t>Tovar uchun to'lov, hisob-faktura №966 22.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>244630000</v>
+        <v>878665000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="B161" t="n">
         <v>253</v>
       </c>
       <c r="C161" s="2" t="n">
-        <v>123325000</v>
+        <v>14666000</v>
       </c>
       <c r="D161" s="2" t="n"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Bekobod Mebel MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>264968280</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20208000071946587001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1638</t>
+          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>121305000</v>
+        <v>863999000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B162" t="n">
         <v>254</v>
       </c>
       <c r="C162" s="2" t="n"/>
       <c r="D162" s="2" t="n">
-        <v>31688000</v>
+        <v>10140000</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>372999048</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>20208000377016016001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4594 28.09.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №246/26, QQS 12%</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>152993000</v>
+        <v>874139000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="B163" t="n">
         <v>255</v>
       </c>
       <c r="C163" s="2" t="n"/>
       <c r="D163" s="2" t="n">
-        <v>25432000</v>
+        <v>23470000</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Guliston Agro AJ</t>
+          <t>Nurafshon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>311518277</t>
+          <t>299904893</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>20208000026703389001</t>
+          <t>20208000701601614001</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9467 28.09.2026, QQS bilan</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1727 25.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>178425000</v>
+        <v>897609000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="B164" t="n">
         <v>256</v>
       </c>
       <c r="C164" s="2" t="n"/>
       <c r="D164" s="2" t="n">
-        <v>15732000</v>
+        <v>15776000</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Guliston Tikuv MChJ</t>
+          <t>Sharq Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>372999048</t>
+          <t>360269719</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>20208000377016016001</t>
+          <t>20208000398158286001</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №299/26, НДС 12%</t>
+          <t>Shartnoma №285/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>194157000</v>
+        <v>913385000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="B165" t="n">
         <v>257</v>
       </c>
-      <c r="C165" s="2" t="n">
-        <v>5508000</v>
-      </c>
-      <c r="D165" s="2" t="n"/>
+      <c r="C165" s="2" t="n"/>
+      <c r="D165" s="2" t="n">
+        <v>11101000</v>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Bunyodkor Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>248495020</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>20208000034886665001</t>
+          <t>20208000108981487001</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -6806,77 +6806,77 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov sentyabr</t>
+          <t>Shartnoma №107/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>188649000</v>
+        <v>924486000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="B166" t="n">
         <v>258</v>
       </c>
-      <c r="C166" s="2" t="n">
-        <v>18194000</v>
-      </c>
-      <c r="D166" s="2" t="n"/>
+      <c r="C166" s="2" t="n"/>
+      <c r="D166" s="2" t="n">
+        <v>8749000</v>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Namangan Moy MChJ</t>
+          <t>Nurafshon Avto Savdo XK</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>321812203</t>
+          <t>299904893</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>20208000102858181001</t>
+          <t>20208000701601614001</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №174/26, QQS bilan</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №5815</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>170455000</v>
+        <v>933235000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="B167" t="n">
         <v>259</v>
       </c>
       <c r="C167" s="2" t="n">
-        <v>44194000</v>
+        <v>43908000</v>
       </c>
       <c r="D167" s="2" t="n"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Xiva Polimer AJ</t>
+          <t>Ziyo Dori-Darmon XK</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>376088511</t>
+          <t>379231023</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>20208000833756295001</t>
+          <t>20208000827805746001</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -6886,151 +6886,431 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8770</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №87/26</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>126261000</v>
+        <v>889327000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
-        <v>46294</v>
+        <v>46293</v>
       </c>
       <c r="B168" t="n">
         <v>260</v>
       </c>
       <c r="C168" s="2" t="n"/>
       <c r="D168" s="2" t="n">
-        <v>76679000</v>
+        <v>11110000</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Olmaliq Metall Servis XK</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>325999899</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000699838757001</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №5248 ОТ 29.09.2026, В Т.Ч. НДС 12%</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №4036</t>
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>202940000</v>
+        <v>900437000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="B169" t="n">
         <v>261</v>
       </c>
       <c r="C169" s="2" t="n"/>
       <c r="D169" s="2" t="n">
-        <v>13760000</v>
+        <v>10748000</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Oydin Yog'och XK</t>
+          <t>Qarshi Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>252112210</t>
+          <t>211221046</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>20208000621258290001</t>
+          <t>20208000125829007001</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №207/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №178/26 от 28.09.2026</t>
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>216700000</v>
+        <v>911185000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="B170" t="n">
         <v>262</v>
       </c>
       <c r="C170" s="2" t="n">
-        <v>300000</v>
+        <v>5508000</v>
       </c>
       <c r="D170" s="2" t="n"/>
       <c r="E170" t="inlineStr">
         <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>20208000827594500001</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Elektr energiyasi uchun to'lov</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>905677000</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B171" t="n">
+        <v>263</v>
+      </c>
+      <c r="C171" s="2" t="n">
+        <v>147360000</v>
+      </c>
+      <c r="D171" s="2" t="n"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Guliston Avto Ehtiyot MChJ</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>322394072</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>20208000620763419001</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №84/26</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>758317000</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B172" t="n">
+        <v>264</v>
+      </c>
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n">
+        <v>17052000</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Qarshi Yog' Zavodi MChJ</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>211221046</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>20208000125829007001</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №299/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>775369000</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B173" t="n">
+        <v>265</v>
+      </c>
+      <c r="C173" s="2" t="n"/>
+      <c r="D173" s="2" t="n">
+        <v>10997000</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Qarshi Yog' Zavodi MChJ</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>211221046</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>20208000125829007001</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №30/26, QQS 12%</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>786366000</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B174" t="n">
+        <v>266</v>
+      </c>
+      <c r="C174" s="2" t="n">
+        <v>214422000</v>
+      </c>
+      <c r="D174" s="2" t="n"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Angren Logistik MChJ</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>266155988</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>20208000649237110001</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Tovarlar uchun to'lov h/f №3716</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>571944000</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B175" t="n">
+        <v>267</v>
+      </c>
+      <c r="C175" s="2" t="n"/>
+      <c r="D175" s="2" t="n">
+        <v>21800000</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Nurafshon Avto Savdo XK</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>299904893</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>20208000701601614001</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №4352 30.09.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>593744000</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B176" t="n">
+        <v>268</v>
+      </c>
+      <c r="C176" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D176" s="2" t="n"/>
+      <c r="E176" t="inlineStr">
+        <is>
           <t>Bodomzor Bank ATB</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
+      <c r="G176" t="inlineStr">
         <is>
           <t>45994000900000001001</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
+      <c r="H176" t="inlineStr">
         <is>
           <t>01204</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
-        </is>
-      </c>
-      <c r="J170" s="2" t="n">
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Bank xizmati uchun komissiya</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>593444000</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B177" t="n">
+        <v>269</v>
+      </c>
+      <c r="C177" s="2" t="n">
+        <v>377044000</v>
+      </c>
+      <c r="D177" s="2" t="n"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Ziyo Dori-Darmon XK</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>379231023</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>20208000827805746001</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №103/26</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="n">
         <v>216400000</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
+    <row r="178">
+      <c r="A178" t="inlineStr">
         <is>
           <t>Итого обороты:</t>
         </is>
       </c>
-      <c r="C171" s="4" t="n">
-        <v>3591561000</v>
-      </c>
-      <c r="D171" s="4" t="n">
-        <v>3584161000</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
+      <c r="C178" s="4" t="n">
+        <v>3519462000</v>
+      </c>
+      <c r="D178" s="4" t="n">
+        <v>3512062000</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
         <is>
           <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
-      <c r="C172" s="4" t="n">
+      <c r="C179" s="4" t="n">
         <v>216400000</v>
       </c>
-      <c r="D172" s="4" t="n"/>
+      <c r="D179" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
